--- a/hiring_companies_2026-10-26.xlsx
+++ b/hiring_companies_2026-10-26.xlsx
@@ -477,7 +477,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Placements24</t>
+          <t>JustMarkets</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -492,12 +492,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Media Relations Executive | Remote Graduate Marketing Assistant | Remote Restaurant Marketing Specialist | Remote Sports Marketing Strategist</t>
+          <t>Senior Web Designer - Growth &amp; Conversion (Remote)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3889994718485627906</t>
+          <t>https://jooble.org/jdp/7384098453309665600</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Placements24</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JustMarkets</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -524,7 +524,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Placements24</t>
+          <t>JustMarkets</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Media Relations Executive | Remote Graduate Marketing Assistant | Remote Restaurant Marketing Specialist | Remote Sports Marketing Strategist</t>
+          <t>Senior Web Designer - Growth &amp; Conversion (Remote)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3889994718485627906</t>
+          <t>https://jooble.org/jdp/7384098453309665600</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Placements24</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JustMarkets</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Placements24</t>
+          <t>JustMarkets</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -586,12 +586,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Media Relations Executive | Remote Graduate Marketing Assistant | Remote Restaurant Marketing Specialist | Remote Sports Marketing Strategist</t>
+          <t>Senior Web Designer - Growth &amp; Conversion (Remote)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3889994718485627906</t>
+          <t>https://jooble.org/jdp/7384098453309665600</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Placements24</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JustMarkets</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Placements24</t>
+          <t>JustMarkets</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Media Relations Executive | Remote Graduate Marketing Assistant | Remote Restaurant Marketing Specialist | Remote Sports Marketing Strategist</t>
+          <t>Senior Web Designer - Growth &amp; Conversion (Remote)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3889994718485627906</t>
+          <t>https://jooble.org/jdp/7384098453309665600</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Placements24</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JustMarkets</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Placements24</t>
+          <t>JustMarkets</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -680,12 +680,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Media Relations Executive | Remote Graduate Marketing Assistant | Remote Restaurant Marketing Specialist | Remote Sports Marketing Strategist</t>
+          <t>Senior Web Designer - Growth &amp; Conversion (Remote)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3889994718485627906</t>
+          <t>https://jooble.org/jdp/7384098453309665600</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Placements24</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JustMarkets</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Placements24</t>
+          <t>JustMarkets</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -727,12 +727,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Media Relations Executive | Remote Graduate Marketing Assistant | Remote Restaurant Marketing Specialist | Remote Sports Marketing Strategist</t>
+          <t>Senior Web Designer - Growth &amp; Conversion (Remote)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3889994718485627906</t>
+          <t>https://jooble.org/jdp/7384098453309665600</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Placements24</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=JustMarkets</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -759,7 +759,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>DataAnnotation</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Media Producer (REMOTE) at More Perfect Union | Remote Video Editor for Dynamic Social &amp; YouTube Content | Social Media Manager (Remote) at LumiMeds</t>
+          <t>Remote Web UI Designer &amp; AI Design Critique | Visual Web Designer - AI Trainer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-981080416933533193</t>
+          <t>https://jooble.org/jdp/-5916554023069523906</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DataAnnotation</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>DataAnnotation</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -821,12 +821,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Media Producer (REMOTE) at More Perfect Union | Remote Video Editor for Dynamic Social &amp; YouTube Content | Social Media Manager (Remote) at LumiMeds</t>
+          <t>Remote Web UI Designer &amp; AI Design Critique | Visual Web Designer - AI Trainer</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-981080416933533193</t>
+          <t>https://jooble.org/jdp/-5916554023069523906</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DataAnnotation</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -853,7 +853,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>DataAnnotation</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -868,12 +868,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Media Producer (REMOTE) at More Perfect Union | Remote Video Editor for Dynamic Social &amp; YouTube Content | Social Media Manager (Remote) at LumiMeds</t>
+          <t>Remote Web UI Designer &amp; AI Design Critique | Visual Web Designer - AI Trainer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-981080416933533193</t>
+          <t>https://jooble.org/jdp/-5916554023069523906</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DataAnnotation</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -900,7 +900,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>DataAnnotation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Media Producer (REMOTE) at More Perfect Union | Remote Video Editor for Dynamic Social &amp; YouTube Content | Social Media Manager (Remote) at LumiMeds</t>
+          <t>Remote Web UI Designer &amp; AI Design Critique | Visual Web Designer - AI Trainer</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-981080416933533193</t>
+          <t>https://jooble.org/jdp/-5916554023069523906</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DataAnnotation</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>DataAnnotation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -962,12 +962,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Media Producer (REMOTE) at More Perfect Union | Remote Video Editor for Dynamic Social &amp; YouTube Content | Social Media Manager (Remote) at LumiMeds</t>
+          <t>Remote Web UI Designer &amp; AI Design Critique | Visual Web Designer - AI Trainer</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-981080416933533193</t>
+          <t>https://jooble.org/jdp/-5916554023069523906</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DataAnnotation</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -994,7 +994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Feedinkoo: Remote Jobs</t>
+          <t>DataAnnotation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Media Producer (REMOTE) at More Perfect Union | Remote Video Editor for Dynamic Social &amp; YouTube Content | Social Media Manager (Remote) at LumiMeds</t>
+          <t>Remote Web UI Designer &amp; AI Design Critique | Visual Web Designer - AI Trainer</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-981080416933533193</t>
+          <t>https://jooble.org/jdp/-5916554023069523906</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Feedinkoo%3A+Remote+Jobs</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DataAnnotation</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>The US Sun</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1056,12 +1056,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>Senior News Reporter</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6889464187706972303</t>
+          <t>https://jooble.org/jdp/-8328439882069448336</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+US+Sun</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1088,7 +1088,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>The US Sun</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>Senior News Reporter</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6889464187706972303</t>
+          <t>https://jooble.org/jdp/-8328439882069448336</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+US+Sun</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1135,7 +1135,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>The US Sun</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>Senior News Reporter</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6889464187706972303</t>
+          <t>https://jooble.org/jdp/-8328439882069448336</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+US+Sun</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1182,7 +1182,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>The US Sun</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>Senior News Reporter</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6889464187706972303</t>
+          <t>https://jooble.org/jdp/-8328439882069448336</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+US+Sun</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>The US Sun</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1244,12 +1244,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>Senior News Reporter</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6889464187706972303</t>
+          <t>https://jooble.org/jdp/-8328439882069448336</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+US+Sun</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1276,7 +1276,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kenyan Edu</t>
+          <t>The US Sun</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1291,12 +1291,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Web Designer, eCRM</t>
+          <t>Senior News Reporter</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/6889464187706972303</t>
+          <t>https://jooble.org/jdp/-8328439882069448336</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Kenyan+Edu</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=The+US+Sun</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TMC Cleaning Services</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1338,12 +1338,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Telephone sales</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5812948333235596790</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TMC+Cleaning+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1370,7 +1370,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TMC Cleaning Services</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Telephone sales</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5812948333235596790</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TMC+Cleaning+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1417,7 +1417,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TMC Cleaning Services</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Telephone sales</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5812948333235596790</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TMC+Cleaning+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1464,7 +1464,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TMC Cleaning Services</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1479,12 +1479,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Telephone sales</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5812948333235596790</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TMC+Cleaning+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TMC Cleaning Services</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Telephone sales</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5812948333235596790</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TMC+Cleaning+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1558,7 +1558,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TMC Cleaning Services</t>
+          <t>ProSearch</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1573,12 +1573,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Telephone sales</t>
+          <t>Sales Engagement Specialist - Remote</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-5812948333235596790</t>
+          <t>https://jooble.org/jdp/5483630948287254816</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=TMC+Cleaning+Services</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ProSearch</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1605,7 +1605,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Texas Sports Academy</t>
+          <t>Arizona Commerce Authority</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Remote Shortform Video Editor - 60-90s Edits</t>
+          <t>FY'27 Winter-Spring Internship: Digital Media</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3424512256892333382</t>
+          <t>https://jooble.org/jdp/-934441028698123578</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Texas+Sports+Academy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arizona+Commerce+Authority</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1652,7 +1652,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Texas Sports Academy</t>
+          <t>Arizona Commerce Authority</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Remote Shortform Video Editor - 60-90s Edits</t>
+          <t>FY'27 Winter-Spring Internship: Digital Media</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3424512256892333382</t>
+          <t>https://jooble.org/jdp/-934441028698123578</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Texas+Sports+Academy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arizona+Commerce+Authority</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1699,7 +1699,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Texas Sports Academy</t>
+          <t>Arizona Commerce Authority</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Remote Shortform Video Editor - 60-90s Edits</t>
+          <t>FY'27 Winter-Spring Internship: Digital Media</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3424512256892333382</t>
+          <t>https://jooble.org/jdp/-934441028698123578</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Texas+Sports+Academy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arizona+Commerce+Authority</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Texas Sports Academy</t>
+          <t>Arizona Commerce Authority</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Remote Shortform Video Editor - 60-90s Edits</t>
+          <t>FY'27 Winter-Spring Internship: Digital Media</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3424512256892333382</t>
+          <t>https://jooble.org/jdp/-934441028698123578</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Texas+Sports+Academy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arizona+Commerce+Authority</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1793,7 +1793,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Texas Sports Academy</t>
+          <t>Arizona Commerce Authority</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Remote Shortform Video Editor - 60-90s Edits</t>
+          <t>FY'27 Winter-Spring Internship: Digital Media</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3424512256892333382</t>
+          <t>https://jooble.org/jdp/-934441028698123578</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Texas+Sports+Academy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arizona+Commerce+Authority</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Texas Sports Academy</t>
+          <t>Arizona Commerce Authority</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1855,12 +1855,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Remote Shortform Video Editor - 60-90s Edits</t>
+          <t>FY'27 Winter-Spring Internship: Digital Media</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/3424512256892333382</t>
+          <t>https://jooble.org/jdp/-934441028698123578</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Texas+Sports+Academy</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Arizona+Commerce+Authority</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1887,7 +1887,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Fella Health</t>
+          <t>Our National Conversation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Web Designer at AIOS - Remote, $75k-$150k/yr (including equity)</t>
+          <t>Social Media Content Intern</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7837496147851526586</t>
+          <t>https://jooble.org/jdp/-5871802065515966604</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fella+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Our+National+Conversation</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1934,7 +1934,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Fella Health</t>
+          <t>Our National Conversation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Web Designer at AIOS - Remote, $75k-$150k/yr (including equity)</t>
+          <t>Social Media Content Intern</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7837496147851526586</t>
+          <t>https://jooble.org/jdp/-5871802065515966604</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fella+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Our+National+Conversation</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fella Health</t>
+          <t>Our National Conversation</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Web Designer at AIOS - Remote, $75k-$150k/yr (including equity)</t>
+          <t>Social Media Content Intern</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7837496147851526586</t>
+          <t>https://jooble.org/jdp/-5871802065515966604</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fella+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Our+National+Conversation</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2028,7 +2028,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fella Health</t>
+          <t>Our National Conversation</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2043,12 +2043,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Web Designer at AIOS - Remote, $75k-$150k/yr (including equity)</t>
+          <t>Social Media Content Intern</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7837496147851526586</t>
+          <t>https://jooble.org/jdp/-5871802065515966604</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fella+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Our+National+Conversation</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Fella Health</t>
+          <t>LIX, Inc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Web Designer at AIOS - Remote, $75k-$150k/yr (including equity)</t>
+          <t>Territory Sales Manager - East Coast</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7837496147851526586</t>
+          <t>https://jooble.org/jdp/7918992163118458452</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fella+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=LIX%2C+Inc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Fella Health</t>
+          <t>Our National Conversation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Web Designer at AIOS - Remote, $75k-$150k/yr (including equity)</t>
+          <t>Social Media Content Intern</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-7837496147851526586</t>
+          <t>https://jooble.org/jdp/-5871802065515966604</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fella+Health</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Our+National+Conversation</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2169,7 +2169,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Koppert Beheer</t>
+          <t>SPECTRAFORCE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2184,22 +2184,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ornamental IPM Territory Sales Consultant - Florida (Remote)</t>
+          <t>Recruitment Marketing Specialist</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2432662687784717021</t>
+          <t>https://jooble.org/jdp/-3863414848677880416</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Koppert+Beheer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SPECTRAFORCE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2216,7 +2216,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Koppert Beheer</t>
+          <t>SPECTRAFORCE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2231,22 +2231,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ornamental IPM Territory Sales Consultant - Florida (Remote)</t>
+          <t>Recruitment Marketing Specialist</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2432662687784717021</t>
+          <t>https://jooble.org/jdp/-3863414848677880416</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Koppert+Beheer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SPECTRAFORCE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2263,7 +2263,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Koppert Beheer</t>
+          <t>TriMed</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ornamental IPM Territory Sales Consultant - Florida (Remote)</t>
+          <t>Associate Brand Manager</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2432662687784717021</t>
+          <t>https://jooble.org/jdp/7604964535340805826</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Koppert+Beheer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=TriMed</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2310,7 +2310,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Koppert Beheer</t>
+          <t>SPECTRAFORCE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Ornamental IPM Territory Sales Consultant - Florida (Remote)</t>
+          <t>Recruitment Marketing Specialist</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2432662687784717021</t>
+          <t>https://jooble.org/jdp/-3863414848677880416</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Koppert+Beheer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SPECTRAFORCE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2357,7 +2357,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Koppert Beheer</t>
+          <t>Our National Conversation</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Ornamental IPM Territory Sales Consultant - Florida (Remote)</t>
+          <t>Social Media Content Intern</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2432662687784717021</t>
+          <t>https://jooble.org/jdp/-5871802065515966604</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Koppert+Beheer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Our+National+Conversation</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2404,7 +2404,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Koppert Beheer</t>
+          <t>SPECTRAFORCE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2419,22 +2419,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Ornamental IPM Territory Sales Consultant - Florida (Remote)</t>
+          <t>Recruitment Marketing Specialist</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2432662687784717021</t>
+          <t>https://jooble.org/jdp/-3863414848677880416</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Koppert+Beheer</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SPECTRAFORCE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2451,7 +2451,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Ticket Teams LLC</t>
+          <t>I3 INFOTEK INC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2466,22 +2466,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Remote Commission Sales Specialist | Remote High-Ticket Enrollment Sales Specialist | Remote High-Ticket Sales Enrollment Specialist | Remote High-Ticket Sales Executive (Uncapped Commission)</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4481162708743371564</t>
+          <t>https://jooble.org/jdp/148239537214377370</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=High+Ticket+Teams+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=I3+INFOTEK+INC</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2498,7 +2498,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Ticket Teams LLC</t>
+          <t>I3 INFOTEK INC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2513,22 +2513,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Remote Commission Sales Specialist | Remote High-Ticket Enrollment Sales Specialist | Remote High-Ticket Sales Enrollment Specialist | Remote High-Ticket Sales Executive (Uncapped Commission)</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4481162708743371564</t>
+          <t>https://jooble.org/jdp/148239537214377370</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=High+Ticket+Teams+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=I3+INFOTEK+INC</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2545,7 +2545,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>High Ticket Teams LLC</t>
+          <t>SPECTRAFORCE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2560,22 +2560,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Remote Commission Sales Specialist | Remote High-Ticket Enrollment Sales Specialist | Remote High-Ticket Sales Enrollment Specialist | Remote High-Ticket Sales Executive (Uncapped Commission)</t>
+          <t>Recruitment Marketing Specialist</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4481162708743371564</t>
+          <t>https://jooble.org/jdp/-3863414848677880416</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=High+Ticket+Teams+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SPECTRAFORCE</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>High Ticket Teams LLC</t>
+          <t>I3 INFOTEK INC</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2607,22 +2607,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Remote Commission Sales Specialist | Remote High-Ticket Enrollment Sales Specialist | Remote High-Ticket Sales Enrollment Specialist | Remote High-Ticket Sales Executive (Uncapped Commission)</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4481162708743371564</t>
+          <t>https://jooble.org/jdp/148239537214377370</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=High+Ticket+Teams+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=I3+INFOTEK+INC</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2639,7 +2639,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>High Ticket Teams LLC</t>
+          <t>SPECTRAFORCE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2654,22 +2654,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Remote Commission Sales Specialist | Remote High-Ticket Enrollment Sales Specialist | Remote High-Ticket Sales Enrollment Specialist | Remote High-Ticket Sales Executive (Uncapped Commission)</t>
+          <t>Recruitment Marketing Specialist</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4481162708743371564</t>
+          <t>https://jooble.org/jdp/-3863414848677880416</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=High+Ticket+Teams+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=SPECTRAFORCE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2686,7 +2686,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Ticket Teams LLC</t>
+          <t>I3 INFOTEK INC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2701,22 +2701,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Remote Commission Sales Specialist | Remote High-Ticket Enrollment Sales Specialist | Remote High-Ticket Sales Enrollment Specialist | Remote High-Ticket Sales Executive (Uncapped Commission) | Remote</t>
+          <t>Social Media Manager</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/4481162708743371564</t>
+          <t>https://jooble.org/jdp/148239537214377370</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=High+Ticket+Teams+LLC</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=I3+INFOTEK+INC</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2733,7 +2733,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AOCUSA</t>
+          <t>BenefitHub</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2748,22 +2748,22 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Remote Territory Sales Rep Lubricants | Territory Lubricants Sales Rep (Remote + Benefits)</t>
+          <t>Director, Newsletter &amp; Email Marketing (REMOTE)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2096973289082124799</t>
+          <t>https://jooble.org/jdp/-1423316940757329276</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AOCUSA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=BenefitHub</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2780,7 +2780,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AOCUSA</t>
+          <t>BenefitHub</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Remote Territory Sales Rep Lubricants | Territory Lubricants Sales Rep (Remote + Benefits)</t>
+          <t>Director, Newsletter &amp; Email Marketing (REMOTE)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://jooble.org/jdp/-2096973289082124799</t>
+          <t>https://jooble.org/jdp/-1423316940757329276</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-10-25</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=AOCUSA</t>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=BenefitHub</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
